--- a/data/trans_camb/P2A_lim_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,25; 14,49</t>
+          <t>4,07; 13,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 8,18</t>
+          <t>0,34; 8,36</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 11,71</t>
+          <t>2,54; 11,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,92; 19,99</t>
+          <t>8,79; 19,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 13,83</t>
+          <t>4,6; 14,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,77; 14,67</t>
+          <t>6,93; 15,43</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,92; 15,26</t>
+          <t>7,75; 14,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 9,7</t>
+          <t>3,23; 9,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 12,24</t>
+          <t>5,6; 11,89</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,23; 525,05</t>
+          <t>63,1; 564,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,73; 328,01</t>
+          <t>-10,94; 314,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,99; 509,05</t>
+          <t>25,38; 408,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>170,73; 1055,75</t>
+          <t>158,12; 1095,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>77,43; 767,96</t>
+          <t>81,22; 836,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>125,21; 837,93</t>
+          <t>107,58; 819,4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>144,97; 599,57</t>
+          <t>148,11; 588,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>68,2; 401,83</t>
+          <t>54,76; 358,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>108,85; 457,6</t>
+          <t>100,95; 470,72</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 3,89</t>
+          <t>-3,86; 4,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,69; -3,24</t>
+          <t>-9,19; -2,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,78; 14,85</t>
+          <t>4,23; 14,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 3,78</t>
+          <t>-4,4; 3,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,17; -2,14</t>
+          <t>-8,62; -1,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,46; 11,65</t>
+          <t>3,85; 11,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 2,43</t>
+          <t>-3,05; 2,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,07; -3,41</t>
+          <t>-8,01; -3,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 11,84</t>
+          <t>5,41; 11,7</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-35,74; 47,45</t>
+          <t>-33,35; 56,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-78,42; -33,21</t>
+          <t>-76,69; -30,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,68; 178,3</t>
+          <t>35,09; 187,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,29; 42,27</t>
+          <t>-34,39; 40,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,03; -20,61</t>
+          <t>-68,26; -18,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,41; 133,25</t>
+          <t>30,9; 134,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,42; 25,54</t>
+          <t>-24,97; 28,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,7; -33,41</t>
+          <t>-68,02; -36,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,11; 130,39</t>
+          <t>47,82; 130,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 11,33</t>
+          <t>2,97; 10,98</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 1,97</t>
+          <t>-2,99; 1,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,19; 17,83</t>
+          <t>9,34; 17,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 10,18</t>
+          <t>2,8; 10,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 4,33</t>
+          <t>-1,23; 4,57</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,58; 13,51</t>
+          <t>6,7; 13,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 9,67</t>
+          <t>3,95; 9,55</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 2,15</t>
+          <t>-1,45; 2,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 14,37</t>
+          <t>8,95; 14,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>64,8; 707,63</t>
+          <t>48,58; 605,54</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-77,14; 142,57</t>
+          <t>-73,86; 143,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>185,02; 1164,63</t>
+          <t>192,72; 1026,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42,24; 527,22</t>
+          <t>56,82; 548,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-37,06; 236,61</t>
+          <t>-35,18; 280,41</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>118,57; 738,89</t>
+          <t>115,66; 752,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>99,64; 472,52</t>
+          <t>84,42; 434,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-43,26; 107,58</t>
+          <t>-36,9; 112,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>212,24; 730,56</t>
+          <t>206,69; 713,71</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 5,06</t>
+          <t>-2,32; 5,16</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,26; 9,67</t>
+          <t>1,2; 9,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 7,37</t>
+          <t>-1,11; 7,33</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 11,43</t>
+          <t>3,26; 11,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 11,87</t>
+          <t>3,53; 11,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 3,22</t>
+          <t>-3,64; 3,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 7,64</t>
+          <t>1,6; 7,14</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 9,17</t>
+          <t>3,41; 9,91</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 3,57</t>
+          <t>-2,06; 3,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-30,37; 132,59</t>
+          <t>-32,58; 130,38</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,1; 240,0</t>
+          <t>13,18; 239,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-30,55; 170,79</t>
+          <t>-18,63; 182,99</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32,25; 266,15</t>
+          <t>41,05; 287,33</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,6; 272,81</t>
+          <t>42,31; 288,43</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,66; 75,21</t>
+          <t>-49,74; 77,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,95; 164,06</t>
+          <t>21,73; 159,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>50,87; 197,66</t>
+          <t>46,68; 212,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 77,45</t>
+          <t>-28,11; 80,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,19; 18,25</t>
+          <t>4,23; 18,75</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,01; 4,03</t>
+          <t>-6,76; 4,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 3,47</t>
+          <t>-6,38; 4,31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 17,46</t>
+          <t>2,35; 17,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 1,09</t>
+          <t>-10,12; 1,79</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,18; 1,27</t>
+          <t>-11,59; 1,02</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,04; 15,79</t>
+          <t>5,64; 15,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 1,29</t>
+          <t>-7,38; 1,2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 1,09</t>
+          <t>-7,49; 0,57</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>30,85; 259,47</t>
+          <t>26,14; 252,35</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-56,55; 55,62</t>
+          <t>-53,01; 60,22</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 54,02</t>
+          <t>-51,28; 62,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13,52; 187,75</t>
+          <t>12,34; 166,79</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-62,69; 13,98</t>
+          <t>-63,15; 24,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-64,78; 12,37</t>
+          <t>-67,21; 7,65</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,83; 172,17</t>
+          <t>38,86; 165,66</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-52,29; 15,55</t>
+          <t>-52,1; 13,82</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 11,71</t>
+          <t>-54,62; 5,92</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,06</t>
+          <t>3,08; 9,94</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,88; 12,94</t>
+          <t>4,87; 13,34</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18,46; 28,47</t>
+          <t>18,33; 28,14</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,73; 14,76</t>
+          <t>5,48; 14,52</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,37; 13,34</t>
+          <t>4,69; 13,7</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,55; 25,52</t>
+          <t>16,3; 25,49</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,51; 11,46</t>
+          <t>5,55; 11,42</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>6,02; 12,15</t>
+          <t>5,89; 12,31</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18,99; 25,68</t>
+          <t>18,74; 25,22</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>87,12; 2190,68</t>
+          <t>92,89; 1983,2</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>128,87; 2491,12</t>
+          <t>145,38; 2331,6</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>589,09; 6722,11</t>
+          <t>572,34; 6623,09</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>109,75; 929,39</t>
+          <t>105,78; 847,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>85,19; 826,18</t>
+          <t>87,48; 822,98</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>320,21; 1637,17</t>
+          <t>324,69; 1584,66</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>158,52; 837,8</t>
+          <t>168,49; 820,45</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>163,37; 840,85</t>
+          <t>170,67; 844,31</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>534,83; 1871,1</t>
+          <t>559,39; 1994,67</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 4,11</t>
+          <t>-1,66; 4,13</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 1,18</t>
+          <t>-4,45; 1,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,04; 12,27</t>
+          <t>5,15; 12,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 4,53</t>
+          <t>-2,23; 4,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 2,27</t>
+          <t>-3,66; 2,41</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,33; 62,46</t>
+          <t>9,52; 62,83</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,64</t>
+          <t>-0,96; 3,4</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 1,13</t>
+          <t>-3,06; 1,1</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8,88; 48,51</t>
+          <t>8,98; 50,7</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 74,01</t>
+          <t>-21,75; 78,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-52,48; 21,54</t>
+          <t>-53,42; 20,64</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>58,56; 221,2</t>
+          <t>57,45; 213,56</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 71,92</t>
+          <t>-24,8; 72,35</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-36,8; 35,4</t>
+          <t>-39,36; 39,26</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>109,95; 987,79</t>
+          <t>114,1; 1145,39</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 55,34</t>
+          <t>-11,38; 53,58</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 16,98</t>
+          <t>-36,15; 18,52</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>113,79; 694,02</t>
+          <t>117,92; 750,83</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,62</t>
+          <t>-2,98; 2,68</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,63; 3,54</t>
+          <t>-2,79; 3,19</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 0,51</t>
+          <t>-6,48; 0,78</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 0,37</t>
+          <t>-5,98; -0,11</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 0,51</t>
+          <t>-6,16; 0,41</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,99</t>
+          <t>-4,92; 0,77</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,34</t>
+          <t>-3,84; 0,36</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 1,03</t>
+          <t>-3,67; 0,95</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,51; -0,34</t>
+          <t>-5,91; -0,2</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-31,08; 38,72</t>
+          <t>-31,63; 39,25</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-27,06; 52,69</t>
+          <t>-27,53; 47,02</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-69,48; 6,01</t>
+          <t>-66,38; 10,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 5,45</t>
+          <t>-45,74; -0,62</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-42,42; 5,46</t>
+          <t>-45,9; 3,83</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-35,36; 10,27</t>
+          <t>-36,68; 7,94</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-33,82; 3,98</t>
+          <t>-34,82; 3,84</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-29,41; 11,97</t>
+          <t>-32,31; 11,4</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-59,94; -4,45</t>
+          <t>-54,96; -2,71</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,3</t>
+          <t>1,46; 4,22</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 1,73</t>
+          <t>-1,02; 1,57</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,34; 8,03</t>
+          <t>3,16; 8,11</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,86</t>
+          <t>2,08; 4,94</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 2,09</t>
+          <t>-0,7; 2,16</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,29; 24,61</t>
+          <t>5,37; 25,2</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,16</t>
+          <t>2,26; 4,15</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,41</t>
+          <t>-0,44; 1,6</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,6; 20,5</t>
+          <t>5,62; 18,78</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>20,37; 70,69</t>
+          <t>19,79; 70,89</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 28,49</t>
+          <t>-13,91; 25,86</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>47,85; 127,85</t>
+          <t>48,36; 132,68</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>22,41; 65,67</t>
+          <t>23,38; 67,25</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 28,79</t>
+          <t>-8,54; 28,77</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>64,3; 322,65</t>
+          <t>63,86; 312,37</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,81; 60,41</t>
+          <t>28,79; 60,26</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 20,43</t>
+          <t>-5,7; 22,29</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>74,06; 262,23</t>
+          <t>75,31; 258,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_lim_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6,98</t>
+          <t>6,45</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,89</t>
+          <t>9,93</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8,87</t>
+          <t>8,18</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,07; 13,95</t>
+          <t>4,02; 13,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,34; 8,36</t>
+          <t>-0,28; 8,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 11,41</t>
+          <t>2,08; 10,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 19,58</t>
+          <t>8,93; 19,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 14,17</t>
+          <t>5,02; 13,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 15,43</t>
+          <t>6,14; 13,59</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 14,89</t>
+          <t>7,43; 14,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,23; 9,69</t>
+          <t>3,46; 9,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,6; 11,89</t>
+          <t>5,33; 11,07</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>164,33%</t>
+          <t>151,88%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>335,47%</t>
+          <t>305,97%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>236,05%</t>
+          <t>217,53%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>63,1; 564,98</t>
+          <t>62,24; 616,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,94; 314,71</t>
+          <t>-7,75; 322,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,38; 408,13</t>
+          <t>29,3; 459,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>158,12; 1095,73</t>
+          <t>147,63; 1067,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,22; 836,58</t>
+          <t>93,07; 778,62</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>107,58; 819,4</t>
+          <t>107,32; 742,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>148,11; 588,12</t>
+          <t>136,22; 565,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>54,76; 358,38</t>
+          <t>63,29; 362,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>100,95; 470,72</t>
+          <t>95,3; 433,04</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,22</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,84</t>
+          <t>7,82</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>8,47</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 4,22</t>
+          <t>-4,55; 3,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,19; -2,68</t>
+          <t>-9,95; -2,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 14,59</t>
+          <t>4,11; 13,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 3,52</t>
+          <t>-4,68; 3,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,62; -1,67</t>
+          <t>-8,66; -2,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 11,72</t>
+          <t>3,91; 11,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,52</t>
+          <t>-3,08; 2,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,01; -3,34</t>
+          <t>-7,88; -3,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 11,7</t>
+          <t>5,42; 11,51</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,25%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-33,35; 56,57</t>
+          <t>-36,17; 46,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-76,69; -30,46</t>
+          <t>-77,72; -33,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35,09; 187,43</t>
+          <t>32,36; 175,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,39; 40,63</t>
+          <t>-35,11; 39,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-68,26; -18,08</t>
+          <t>-68,25; -19,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,9; 134,19</t>
+          <t>28,15; 129,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 28,39</t>
+          <t>-25,39; 31,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-68,02; -36,92</t>
+          <t>-68,12; -36,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,82; 130,92</t>
+          <t>45,04; 126,75</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13,45</t>
+          <t>13,29</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,98</t>
+          <t>9,87</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11,63</t>
+          <t>11,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 10,98</t>
+          <t>3,06; 11,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 1,75</t>
+          <t>-3,23; 1,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,34; 17,95</t>
+          <t>9,74; 18,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 10,25</t>
+          <t>2,93; 10,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 4,57</t>
+          <t>-1,3; 4,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 13,5</t>
+          <t>6,48; 13,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,95; 9,55</t>
+          <t>3,86; 9,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 2,26</t>
+          <t>-1,77; 2,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8,95; 14,38</t>
+          <t>9,1; 14,41</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>475,94%</t>
+          <t>470,22%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>319,33%</t>
+          <t>315,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>390,35%</t>
+          <t>385,28%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>48,58; 605,54</t>
+          <t>68,09; 737,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-73,86; 143,11</t>
+          <t>-77,69; 139,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>192,72; 1026,73</t>
+          <t>213,09; 1155,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>56,82; 548,11</t>
+          <t>55,05; 555,83</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,18; 280,41</t>
+          <t>-35,43; 221,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>115,66; 752,03</t>
+          <t>119,48; 729,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>84,42; 434,22</t>
+          <t>87,09; 460,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 112,16</t>
+          <t>-44,6; 99,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>206,69; 713,71</t>
+          <t>206,8; 724,96</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>2,72</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>1,86</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 5,16</t>
+          <t>-1,91; 5,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,2; 9,54</t>
+          <t>1,4; 9,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 7,33</t>
+          <t>-1,34; 7,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,26; 11,58</t>
+          <t>3,37; 11,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 11,89</t>
+          <t>3,51; 12,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 3,25</t>
+          <t>-1,9; 4,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 7,14</t>
+          <t>1,66; 7,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 9,91</t>
+          <t>3,46; 9,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 3,8</t>
+          <t>-0,43; 4,68</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-2,37%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-32,58; 130,38</t>
+          <t>-28,84; 138,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,18; 239,2</t>
+          <t>15,11; 242,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 182,99</t>
+          <t>-23,8; 179,8</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41,05; 287,33</t>
+          <t>36,97; 279,63</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>42,31; 288,43</t>
+          <t>45,29; 303,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,74; 77,99</t>
+          <t>-29,29; 107,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,73; 159,54</t>
+          <t>21,43; 161,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>46,68; 212,42</t>
+          <t>48,43; 225,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,11; 80,99</t>
+          <t>-7,29; 102,81</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,6</t>
+          <t>-2,03</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,07</t>
+          <t>-2,02</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,81</t>
+          <t>-1,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,23; 18,75</t>
+          <t>3,48; 18,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 4,17</t>
+          <t>-6,67; 3,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 4,31</t>
+          <t>-7,58; 2,82</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,35; 17,03</t>
+          <t>2,58; 17,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 1,79</t>
+          <t>-11,24; 1,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,59; 1,02</t>
+          <t>-7,88; 2,64</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,64; 15,72</t>
+          <t>4,72; 15,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 1,2</t>
+          <t>-7,2; 0,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 0,57</t>
+          <t>-5,82; 2,15</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-16,22%</t>
+          <t>-20,52%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-31,58%</t>
+          <t>-15,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-24,59%</t>
+          <t>-17,27%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>26,14; 252,35</t>
+          <t>24,82; 255,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,01; 60,22</t>
+          <t>-55,12; 55,73</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-51,28; 62,7</t>
+          <t>-56,13; 43,45</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12,34; 166,79</t>
+          <t>10,26; 172,33</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-63,15; 24,74</t>
+          <t>-65,97; 15,11</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-67,21; 7,65</t>
+          <t>-44,81; 29,45</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,86; 165,66</t>
+          <t>35,06; 167,82</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-52,1; 13,82</t>
+          <t>-52,54; 7,49</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,62; 5,92</t>
+          <t>-40,97; 24,43</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23,21</t>
+          <t>23,08</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,13</t>
+          <t>20,73</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>22,17</t>
+          <t>21,9</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,08; 9,94</t>
+          <t>3,17; 10,04</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>4,87; 13,34</t>
+          <t>4,85; 13,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18,33; 28,14</t>
+          <t>18,48; 27,51</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5,48; 14,52</t>
+          <t>5,8; 14,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,69; 13,7</t>
+          <t>4,6; 13,79</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,3; 25,49</t>
+          <t>16,13; 24,97</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,55; 11,42</t>
+          <t>5,58; 11,44</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,31</t>
+          <t>5,96; 11,78</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18,74; 25,22</t>
+          <t>18,84; 25,23</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1589,6%</t>
+          <t>1580,59%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>718,13%</t>
+          <t>704,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1001,2%</t>
+          <t>989,2%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>92,89; 1983,2</t>
+          <t>90,27; 2023,57</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>145,38; 2331,6</t>
+          <t>152,06; 2674,98</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>572,34; 6623,09</t>
+          <t>593,48; 6699,8</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>105,78; 847,39</t>
+          <t>105,66; 864,0</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>87,48; 822,98</t>
+          <t>75,99; 728,87</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>324,69; 1584,66</t>
+          <t>330,35; 1666,63</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>168,49; 820,45</t>
+          <t>161,01; 852,39</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>170,67; 844,31</t>
+          <t>162,67; 843,15</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>559,39; 1994,67</t>
+          <t>548,27; 1891,36</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8,8</t>
+          <t>9,13</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>30,33</t>
+          <t>11,79</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21,32</t>
+          <t>10,53</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 4,13</t>
+          <t>-1,82; 4,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 1,08</t>
+          <t>-4,18; 1,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>5,15; 12,38</t>
+          <t>5,84; 13,19</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,54</t>
+          <t>-2,08; 4,29</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 2,41</t>
+          <t>-3,61; 2,65</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>9,52; 62,83</t>
+          <t>8,1; 15,36</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,4</t>
+          <t>-0,95; 3,55</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 1,1</t>
+          <t>-2,89; 1,12</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>8,98; 50,7</t>
+          <t>8,14; 13,32</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>126,04%</t>
+          <t>130,88%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>385,05%</t>
+          <t>149,63%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>286,73%</t>
+          <t>141,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-21,75; 78,14</t>
+          <t>-23,47; 77,32</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-53,42; 20,64</t>
+          <t>-49,87; 24,14</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>57,45; 213,56</t>
+          <t>56,02; 228,18</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 72,35</t>
+          <t>-21,48; 68,41</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,36; 39,26</t>
+          <t>-39,38; 44,1</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>114,1; 1145,39</t>
+          <t>80,16; 246,5</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,38; 53,58</t>
+          <t>-11,13; 55,35</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 18,52</t>
+          <t>-34,26; 17,76</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>117,92; 750,83</t>
+          <t>90,82; 214,48</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,46</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,5</t>
+          <t>-1,07</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 2,68</t>
+          <t>-3,17; 2,54</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 3,19</t>
+          <t>-2,47; 3,22</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 0,78</t>
+          <t>-3,28; 2,27</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-5,98; -0,11</t>
+          <t>-6,13; 0,01</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,16; 0,41</t>
+          <t>-5,52; 0,35</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,77</t>
+          <t>-4,46; 1,41</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,36</t>
+          <t>-3,66; 0,52</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,95</t>
+          <t>-3,27; 1,11</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-5,91; -0,2</t>
+          <t>-3,35; 1,01</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-29,78%</t>
+          <t>-5,36%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-16,63%</t>
+          <t>-14,11%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-24,96%</t>
+          <t>-10,66%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-31,63; 39,25</t>
+          <t>-32,9; 38,66</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-27,53; 47,02</t>
+          <t>-25,43; 47,51</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-66,38; 10,01</t>
+          <t>-34,35; 32,96</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-45,74; -0,62</t>
+          <t>-45,88; 0,84</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 3,83</t>
+          <t>-41,83; 5,39</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-36,68; 7,94</t>
+          <t>-34,0; 13,62</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 3,84</t>
+          <t>-33,04; 6,05</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-32,31; 11,4</t>
+          <t>-30,03; 12,38</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-54,96; -2,71</t>
+          <t>-29,88; 11,06</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6,2</t>
+          <t>6,88</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10,54</t>
+          <t>6,46</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8,46</t>
+          <t>6,67</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,22</t>
+          <t>1,45; 4,24</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,57</t>
+          <t>-0,89; 1,7</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,11</t>
+          <t>5,36; 8,39</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,94</t>
+          <t>2,02; 4,96</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,16</t>
+          <t>-0,57; 2,03</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,37; 25,2</t>
+          <t>5,06; 7,77</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,15</t>
+          <t>2,17; 4,11</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,6</t>
+          <t>-0,39; 1,48</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>5,62; 18,78</t>
+          <t>5,63; 7,76</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>103,25%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>131,01%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>114,93%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>19,79; 70,89</t>
+          <t>19,54; 68,27</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-13,91; 25,86</t>
+          <t>-12,17; 27,67</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>48,36; 132,68</t>
+          <t>72,44; 139,49</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>23,38; 67,25</t>
+          <t>22,48; 65,7</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 28,77</t>
+          <t>-6,88; 27,78</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>63,86; 312,37</t>
+          <t>56,08; 105,59</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>28,79; 60,26</t>
+          <t>27,61; 59,31</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 22,29</t>
+          <t>-5,01; 21,55</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>75,31; 258,01</t>
+          <t>71,56; 113,19</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_lim_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_lim_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con alguna limitación</t>
+          <t>Población que convive con personas con alguna limitación (física, sensorial o psíquica)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
